--- a/projeto/categorias_nibo.xlsx
+++ b/projeto/categorias_nibo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F22E766-4458-4D5B-BEC2-856E692DB8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DD1571-AF98-4B8A-B809-9A9386CA201F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Categoria" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -119,6 +119,12 @@
   </si>
   <si>
     <t>2a456809-2058-43cf-9610-b2ae249dae67</t>
+  </si>
+  <si>
+    <t>Consignado CLT</t>
+  </si>
+  <si>
+    <t>4e5af613-0766-4533-a60b-ea403b7277a5</t>
   </si>
 </sst>
 </file>
@@ -495,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="42.53515625" bestFit="1" customWidth="1"/>
@@ -630,6 +636,14 @@
         <v>31</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B11" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
